--- a/fi_actuals_upload_template.xlsx
+++ b/fi_actuals_upload_template.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R9ec3d9b812754016"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FI Actuals" sheetId="2" r:id="R32fac32a985142b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R7902194b53ca4e44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FI Actuals" sheetId="2" r:id="R3e2d1af106114112"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -31,12 +31,11 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FF0F2F5F"/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,7 +44,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0F2F5F"/>
+        <x:fgColor rgb="FF1D4ED8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0F172A"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -56,29 +60,65 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FIActualsUploadTable" displayName="FIActualsUploadTable" ref="A1:F101" headerRowCount="1">
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="Project"/>
+    <x:tableColumn id="2" name="Employee/Supplier"/>
+    <x:tableColumn id="3" name="Item Date"/>
+    <x:tableColumn id="4" name="Quantity"/>
+    <x:tableColumn id="5" name="UOM"/>
+    <x:tableColumn id="6" name="Location"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -230,66 +270,78 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="72" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="37.880001068115234" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="113.62999725341797" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="12" t="str">
-        <x:v>Financial Tracker FI Actuals Upload Template v3.5</x:v>
-      </x:c>
+      <x:c r="A1" s="8" t="str">
+        <x:v>Financial Tracker FI Actuals Upload Template v3.6</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>FI Upload requires Project, Employee/Supplier, Item Date, Quantity, UOM and Location. Quantity is hours. UOM must contain Hours. Location controls days conversion: IND = 9 hours/day, ANZ = 8 hours/day.</x:v>
+      <x:c r="A2" s="9" t="str">
+        <x:v>Purpose</x:v>
+      </x:c>
+      <x:c r="B2" s="10" t="str">
+        <x:v>Load actual hours into Financial Tracker Actuals.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>Required columns</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="str">
+        <x:v>Project, Employee/Supplier, Item Date, Quantity, UOM and Location.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="str">
+      <x:c r="A4" s="9" t="str">
         <x:v>Project</x:v>
       </x:c>
-      <x:c r="B4" t="str">
-        <x:v>Project code, for example 850141619</x:v>
+      <x:c r="B4" s="10" t="str">
+        <x:v>Project code, e.g. 850141619.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="str">
+      <x:c r="A5" s="9" t="str">
         <x:v>Employee/Supplier</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>Employee or supplier name. Used with Project as the matching key.</x:v>
+      <x:c r="B5" s="10" t="str">
+        <x:v>Employee/resource name. This is matched with Forecast Name.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="str">
+      <x:c r="A6" s="9" t="str">
         <x:v>Item Date</x:v>
       </x:c>
-      <x:c r="B6" t="str">
-        <x:v>Date of the time entry. Used to calculate project week from Dashboard Start Date.</x:v>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Date of the time entry. The app converts this to the correct project week using Dashboard Start Date.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="str">
+      <x:c r="A7" s="9" t="str">
         <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>Number of hours</x:v>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Number of hours.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="str">
+      <x:c r="A8" s="9" t="str">
         <x:v>UOM</x:v>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>Must contain Hours</x:v>
+      <x:c r="B8" s="10" t="str">
+        <x:v>Must contain Hours. Non-Hours rows are skipped.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" t="str">
+      <x:c r="A9" s="9" t="str">
         <x:v>Location</x:v>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>IND or ANZ only</x:v>
+      <x:c r="B9" s="10" t="str">
+        <x:v>IND or ANZ. IND hours are divided by 9; ANZ hours are divided by 8. If omitted in a real FI export, the app derives Location from Forecast where possible.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -301,443 +353,1046 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>Project</x:v>
       </x:c>
-      <x:c r="B1" s="4" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>Employee/Supplier</x:v>
       </x:c>
-      <x:c r="C1" s="4" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>Item Date</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>Quantity</x:v>
       </x:c>
-      <x:c r="E1" s="4" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>UOM</x:v>
       </x:c>
-      <x:c r="F1" s="4" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>Location</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str"/>
       <x:c r="B2" t="str"/>
-      <x:c r="C2" s="8" t="str"/>
-      <x:c r="D2" s="10" t="str"/>
-      <x:c r="E2" t="str"/>
+      <x:c r="C2" s="20" t="str"/>
+      <x:c r="D2" s="22"/>
+      <x:c r="E2" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str"/>
       <x:c r="B3" t="str"/>
-      <x:c r="C3" s="8" t="str"/>
-      <x:c r="D3" s="10" t="str"/>
-      <x:c r="E3" t="str"/>
+      <x:c r="C3" s="20" t="str"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str"/>
       <x:c r="B4" t="str"/>
-      <x:c r="C4" s="8" t="str"/>
-      <x:c r="D4" s="10" t="str"/>
-      <x:c r="E4" t="str"/>
+      <x:c r="C4" s="20" t="str"/>
+      <x:c r="D4" s="22"/>
+      <x:c r="E4" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str"/>
       <x:c r="B5" t="str"/>
-      <x:c r="C5" s="8" t="str"/>
-      <x:c r="D5" s="10" t="str"/>
-      <x:c r="E5" t="str"/>
+      <x:c r="C5" s="20" t="str"/>
+      <x:c r="D5" s="22"/>
+      <x:c r="E5" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str"/>
       <x:c r="B6" t="str"/>
-      <x:c r="C6" s="8" t="str"/>
-      <x:c r="D6" s="10" t="str"/>
-      <x:c r="E6" t="str"/>
+      <x:c r="C6" s="20" t="str"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str"/>
       <x:c r="B7" t="str"/>
-      <x:c r="C7" s="8" t="str"/>
-      <x:c r="D7" s="10" t="str"/>
-      <x:c r="E7" t="str"/>
+      <x:c r="C7" s="20" t="str"/>
+      <x:c r="D7" s="22"/>
+      <x:c r="E7" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str"/>
       <x:c r="B8" t="str"/>
-      <x:c r="C8" s="8" t="str"/>
-      <x:c r="D8" s="10" t="str"/>
-      <x:c r="E8" t="str"/>
+      <x:c r="C8" s="20" t="str"/>
+      <x:c r="D8" s="22"/>
+      <x:c r="E8" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F8" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str"/>
       <x:c r="B9" t="str"/>
-      <x:c r="C9" s="8" t="str"/>
-      <x:c r="D9" s="10" t="str"/>
-      <x:c r="E9" t="str"/>
+      <x:c r="C9" s="20" t="str"/>
+      <x:c r="D9" s="22"/>
+      <x:c r="E9" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F9" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str"/>
       <x:c r="B10" t="str"/>
-      <x:c r="C10" s="8" t="str"/>
-      <x:c r="D10" s="10" t="str"/>
-      <x:c r="E10" t="str"/>
+      <x:c r="C10" s="20" t="str"/>
+      <x:c r="D10" s="22"/>
+      <x:c r="E10" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F10" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str"/>
       <x:c r="B11" t="str"/>
-      <x:c r="C11" s="8" t="str"/>
-      <x:c r="D11" s="10" t="str"/>
-      <x:c r="E11" t="str"/>
+      <x:c r="C11" s="20" t="str"/>
+      <x:c r="D11" s="22"/>
+      <x:c r="E11" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F11" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str"/>
       <x:c r="B12" t="str"/>
-      <x:c r="C12" s="8" t="str"/>
-      <x:c r="D12" s="10" t="str"/>
-      <x:c r="E12" t="str"/>
+      <x:c r="C12" s="20" t="str"/>
+      <x:c r="D12" s="22"/>
+      <x:c r="E12" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F12" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str"/>
       <x:c r="B13" t="str"/>
-      <x:c r="C13" s="8" t="str"/>
-      <x:c r="D13" s="10" t="str"/>
-      <x:c r="E13" t="str"/>
+      <x:c r="C13" s="20" t="str"/>
+      <x:c r="D13" s="22"/>
+      <x:c r="E13" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F13" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str"/>
       <x:c r="B14" t="str"/>
-      <x:c r="C14" s="8" t="str"/>
-      <x:c r="D14" s="10" t="str"/>
-      <x:c r="E14" t="str"/>
+      <x:c r="C14" s="20" t="str"/>
+      <x:c r="D14" s="22"/>
+      <x:c r="E14" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F14" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str"/>
       <x:c r="B15" t="str"/>
-      <x:c r="C15" s="8" t="str"/>
-      <x:c r="D15" s="10" t="str"/>
-      <x:c r="E15" t="str"/>
+      <x:c r="C15" s="20" t="str"/>
+      <x:c r="D15" s="22"/>
+      <x:c r="E15" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F15" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str"/>
       <x:c r="B16" t="str"/>
-      <x:c r="C16" s="8" t="str"/>
-      <x:c r="D16" s="10" t="str"/>
-      <x:c r="E16" t="str"/>
+      <x:c r="C16" s="20" t="str"/>
+      <x:c r="D16" s="22"/>
+      <x:c r="E16" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F16" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str"/>
       <x:c r="B17" t="str"/>
-      <x:c r="C17" s="8" t="str"/>
-      <x:c r="D17" s="10" t="str"/>
-      <x:c r="E17" t="str"/>
+      <x:c r="C17" s="20" t="str"/>
+      <x:c r="D17" s="22"/>
+      <x:c r="E17" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F17" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str"/>
       <x:c r="B18" t="str"/>
-      <x:c r="C18" s="8" t="str"/>
-      <x:c r="D18" s="10" t="str"/>
-      <x:c r="E18" t="str"/>
+      <x:c r="C18" s="20" t="str"/>
+      <x:c r="D18" s="22"/>
+      <x:c r="E18" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F18" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str"/>
       <x:c r="B19" t="str"/>
-      <x:c r="C19" s="8" t="str"/>
-      <x:c r="D19" s="10" t="str"/>
-      <x:c r="E19" t="str"/>
+      <x:c r="C19" s="20" t="str"/>
+      <x:c r="D19" s="22"/>
+      <x:c r="E19" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F19" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="str"/>
       <x:c r="B20" t="str"/>
-      <x:c r="C20" s="8" t="str"/>
-      <x:c r="D20" s="10" t="str"/>
-      <x:c r="E20" t="str"/>
+      <x:c r="C20" s="20" t="str"/>
+      <x:c r="D20" s="22"/>
+      <x:c r="E20" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F20" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="str"/>
       <x:c r="B21" t="str"/>
-      <x:c r="C21" s="8" t="str"/>
-      <x:c r="D21" s="10" t="str"/>
-      <x:c r="E21" t="str"/>
+      <x:c r="C21" s="20" t="str"/>
+      <x:c r="D21" s="22"/>
+      <x:c r="E21" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F21" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="str"/>
       <x:c r="B22" t="str"/>
-      <x:c r="C22" s="8" t="str"/>
-      <x:c r="D22" s="10" t="str"/>
-      <x:c r="E22" t="str"/>
+      <x:c r="C22" s="20" t="str"/>
+      <x:c r="D22" s="22"/>
+      <x:c r="E22" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="str"/>
       <x:c r="B23" t="str"/>
-      <x:c r="C23" s="8" t="str"/>
-      <x:c r="D23" s="10" t="str"/>
-      <x:c r="E23" t="str"/>
+      <x:c r="C23" s="20" t="str"/>
+      <x:c r="D23" s="22"/>
+      <x:c r="E23" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F23" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="str"/>
       <x:c r="B24" t="str"/>
-      <x:c r="C24" s="8" t="str"/>
-      <x:c r="D24" s="10" t="str"/>
-      <x:c r="E24" t="str"/>
+      <x:c r="C24" s="20" t="str"/>
+      <x:c r="D24" s="22"/>
+      <x:c r="E24" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F24" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="str"/>
       <x:c r="B25" t="str"/>
-      <x:c r="C25" s="8" t="str"/>
-      <x:c r="D25" s="10" t="str"/>
-      <x:c r="E25" t="str"/>
+      <x:c r="C25" s="20" t="str"/>
+      <x:c r="D25" s="22"/>
+      <x:c r="E25" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F25" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="str"/>
       <x:c r="B26" t="str"/>
-      <x:c r="C26" s="8" t="str"/>
-      <x:c r="D26" s="10" t="str"/>
-      <x:c r="E26" t="str"/>
+      <x:c r="C26" s="20" t="str"/>
+      <x:c r="D26" s="22"/>
+      <x:c r="E26" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F26" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str"/>
       <x:c r="B27" t="str"/>
-      <x:c r="C27" s="8" t="str"/>
-      <x:c r="D27" s="10" t="str"/>
-      <x:c r="E27" t="str"/>
+      <x:c r="C27" s="20" t="str"/>
+      <x:c r="D27" s="22"/>
+      <x:c r="E27" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F27" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="str"/>
       <x:c r="B28" t="str"/>
-      <x:c r="C28" s="8" t="str"/>
-      <x:c r="D28" s="10" t="str"/>
-      <x:c r="E28" t="str"/>
+      <x:c r="C28" s="20" t="str"/>
+      <x:c r="D28" s="22"/>
+      <x:c r="E28" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F28" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="str"/>
       <x:c r="B29" t="str"/>
-      <x:c r="C29" s="8" t="str"/>
-      <x:c r="D29" s="10" t="str"/>
-      <x:c r="E29" t="str"/>
+      <x:c r="C29" s="20" t="str"/>
+      <x:c r="D29" s="22"/>
+      <x:c r="E29" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F29" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="str"/>
       <x:c r="B30" t="str"/>
-      <x:c r="C30" s="8" t="str"/>
-      <x:c r="D30" s="10" t="str"/>
-      <x:c r="E30" t="str"/>
+      <x:c r="C30" s="20" t="str"/>
+      <x:c r="D30" s="22"/>
+      <x:c r="E30" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F30" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="str"/>
       <x:c r="B31" t="str"/>
-      <x:c r="C31" s="8" t="str"/>
-      <x:c r="D31" s="10" t="str"/>
-      <x:c r="E31" t="str"/>
+      <x:c r="C31" s="20" t="str"/>
+      <x:c r="D31" s="22"/>
+      <x:c r="E31" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F31" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="str"/>
       <x:c r="B32" t="str"/>
-      <x:c r="C32" s="8" t="str"/>
-      <x:c r="D32" s="10" t="str"/>
-      <x:c r="E32" t="str"/>
+      <x:c r="C32" s="20" t="str"/>
+      <x:c r="D32" s="22"/>
+      <x:c r="E32" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F32" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="str"/>
       <x:c r="B33" t="str"/>
-      <x:c r="C33" s="8" t="str"/>
-      <x:c r="D33" s="10" t="str"/>
-      <x:c r="E33" t="str"/>
+      <x:c r="C33" s="20" t="str"/>
+      <x:c r="D33" s="22"/>
+      <x:c r="E33" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F33" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="str"/>
       <x:c r="B34" t="str"/>
-      <x:c r="C34" s="8" t="str"/>
-      <x:c r="D34" s="10" t="str"/>
-      <x:c r="E34" t="str"/>
+      <x:c r="C34" s="20" t="str"/>
+      <x:c r="D34" s="22"/>
+      <x:c r="E34" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F34" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="str"/>
       <x:c r="B35" t="str"/>
-      <x:c r="C35" s="8" t="str"/>
-      <x:c r="D35" s="10" t="str"/>
-      <x:c r="E35" t="str"/>
+      <x:c r="C35" s="20" t="str"/>
+      <x:c r="D35" s="22"/>
+      <x:c r="E35" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F35" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="str"/>
       <x:c r="B36" t="str"/>
-      <x:c r="C36" s="8" t="str"/>
-      <x:c r="D36" s="10" t="str"/>
-      <x:c r="E36" t="str"/>
+      <x:c r="C36" s="20" t="str"/>
+      <x:c r="D36" s="22"/>
+      <x:c r="E36" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F36" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="str"/>
       <x:c r="B37" t="str"/>
-      <x:c r="C37" s="8" t="str"/>
-      <x:c r="D37" s="10" t="str"/>
-      <x:c r="E37" t="str"/>
+      <x:c r="C37" s="20" t="str"/>
+      <x:c r="D37" s="22"/>
+      <x:c r="E37" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F37" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="str"/>
       <x:c r="B38" t="str"/>
-      <x:c r="C38" s="8" t="str"/>
-      <x:c r="D38" s="10" t="str"/>
-      <x:c r="E38" t="str"/>
+      <x:c r="C38" s="20" t="str"/>
+      <x:c r="D38" s="22"/>
+      <x:c r="E38" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F38" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="str"/>
       <x:c r="B39" t="str"/>
-      <x:c r="C39" s="8" t="str"/>
-      <x:c r="D39" s="10" t="str"/>
-      <x:c r="E39" t="str"/>
+      <x:c r="C39" s="20" t="str"/>
+      <x:c r="D39" s="22"/>
+      <x:c r="E39" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F39" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="str"/>
       <x:c r="B40" t="str"/>
-      <x:c r="C40" s="8" t="str"/>
-      <x:c r="D40" s="10" t="str"/>
-      <x:c r="E40" t="str"/>
+      <x:c r="C40" s="20" t="str"/>
+      <x:c r="D40" s="22"/>
+      <x:c r="E40" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F40" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="str"/>
       <x:c r="B41" t="str"/>
-      <x:c r="C41" s="8" t="str"/>
-      <x:c r="D41" s="10" t="str"/>
-      <x:c r="E41" t="str"/>
+      <x:c r="C41" s="20" t="str"/>
+      <x:c r="D41" s="22"/>
+      <x:c r="E41" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F41" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str"/>
       <x:c r="B42" t="str"/>
-      <x:c r="C42" s="8" t="str"/>
-      <x:c r="D42" s="10" t="str"/>
-      <x:c r="E42" t="str"/>
+      <x:c r="C42" s="20" t="str"/>
+      <x:c r="D42" s="22"/>
+      <x:c r="E42" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F42" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str"/>
       <x:c r="B43" t="str"/>
-      <x:c r="C43" s="8" t="str"/>
-      <x:c r="D43" s="10" t="str"/>
-      <x:c r="E43" t="str"/>
+      <x:c r="C43" s="20" t="str"/>
+      <x:c r="D43" s="22"/>
+      <x:c r="E43" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F43" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str"/>
       <x:c r="B44" t="str"/>
-      <x:c r="C44" s="8" t="str"/>
-      <x:c r="D44" s="10" t="str"/>
-      <x:c r="E44" t="str"/>
+      <x:c r="C44" s="20" t="str"/>
+      <x:c r="D44" s="22"/>
+      <x:c r="E44" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F44" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str"/>
       <x:c r="B45" t="str"/>
-      <x:c r="C45" s="8" t="str"/>
-      <x:c r="D45" s="10" t="str"/>
-      <x:c r="E45" t="str"/>
+      <x:c r="C45" s="20" t="str"/>
+      <x:c r="D45" s="22"/>
+      <x:c r="E45" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F45" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str"/>
       <x:c r="B46" t="str"/>
-      <x:c r="C46" s="8" t="str"/>
-      <x:c r="D46" s="10" t="str"/>
-      <x:c r="E46" t="str"/>
+      <x:c r="C46" s="20" t="str"/>
+      <x:c r="D46" s="22"/>
+      <x:c r="E46" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F46" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str"/>
       <x:c r="B47" t="str"/>
-      <x:c r="C47" s="8" t="str"/>
-      <x:c r="D47" s="10" t="str"/>
-      <x:c r="E47" t="str"/>
+      <x:c r="C47" s="20" t="str"/>
+      <x:c r="D47" s="22"/>
+      <x:c r="E47" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F47" t="str"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str"/>
       <x:c r="B48" t="str"/>
-      <x:c r="C48" s="8" t="str"/>
-      <x:c r="D48" s="10" t="str"/>
-      <x:c r="E48" t="str"/>
+      <x:c r="C48" s="20" t="str"/>
+      <x:c r="D48" s="22"/>
+      <x:c r="E48" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F48" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str"/>
       <x:c r="B49" t="str"/>
-      <x:c r="C49" s="8" t="str"/>
-      <x:c r="D49" s="10" t="str"/>
-      <x:c r="E49" t="str"/>
+      <x:c r="C49" s="20" t="str"/>
+      <x:c r="D49" s="22"/>
+      <x:c r="E49" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F49" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str"/>
       <x:c r="B50" t="str"/>
-      <x:c r="C50" s="8" t="str"/>
-      <x:c r="D50" s="10" t="str"/>
-      <x:c r="E50" t="str"/>
+      <x:c r="C50" s="20" t="str"/>
+      <x:c r="D50" s="22"/>
+      <x:c r="E50" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F50" t="str"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str"/>
       <x:c r="B51" t="str"/>
-      <x:c r="C51" s="8" t="str"/>
-      <x:c r="D51" s="10" t="str"/>
-      <x:c r="E51" t="str"/>
+      <x:c r="C51" s="20" t="str"/>
+      <x:c r="D51" s="22"/>
+      <x:c r="E51" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
       <x:c r="F51" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str"/>
+      <x:c r="B52" t="str"/>
+      <x:c r="C52" s="20" t="str"/>
+      <x:c r="D52" s="22"/>
+      <x:c r="E52" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F52" t="str"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str"/>
+      <x:c r="B53" t="str"/>
+      <x:c r="C53" s="20" t="str"/>
+      <x:c r="D53" s="22"/>
+      <x:c r="E53" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F53" t="str"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str"/>
+      <x:c r="B54" t="str"/>
+      <x:c r="C54" s="20" t="str"/>
+      <x:c r="D54" s="22"/>
+      <x:c r="E54" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F54" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str"/>
+      <x:c r="B55" t="str"/>
+      <x:c r="C55" s="20" t="str"/>
+      <x:c r="D55" s="22"/>
+      <x:c r="E55" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F55" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str"/>
+      <x:c r="B56" t="str"/>
+      <x:c r="C56" s="20" t="str"/>
+      <x:c r="D56" s="22"/>
+      <x:c r="E56" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F56" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str"/>
+      <x:c r="B57" t="str"/>
+      <x:c r="C57" s="20" t="str"/>
+      <x:c r="D57" s="22"/>
+      <x:c r="E57" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F57" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str"/>
+      <x:c r="B58" t="str"/>
+      <x:c r="C58" s="20" t="str"/>
+      <x:c r="D58" s="22"/>
+      <x:c r="E58" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F58" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str"/>
+      <x:c r="B59" t="str"/>
+      <x:c r="C59" s="20" t="str"/>
+      <x:c r="D59" s="22"/>
+      <x:c r="E59" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F59" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str"/>
+      <x:c r="B60" t="str"/>
+      <x:c r="C60" s="20" t="str"/>
+      <x:c r="D60" s="22"/>
+      <x:c r="E60" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F60" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str"/>
+      <x:c r="B61" t="str"/>
+      <x:c r="C61" s="20" t="str"/>
+      <x:c r="D61" s="22"/>
+      <x:c r="E61" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F61" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str"/>
+      <x:c r="B62" t="str"/>
+      <x:c r="C62" s="20" t="str"/>
+      <x:c r="D62" s="22"/>
+      <x:c r="E62" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F62" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str"/>
+      <x:c r="B63" t="str"/>
+      <x:c r="C63" s="20" t="str"/>
+      <x:c r="D63" s="22"/>
+      <x:c r="E63" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F63" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str"/>
+      <x:c r="B64" t="str"/>
+      <x:c r="C64" s="20" t="str"/>
+      <x:c r="D64" s="22"/>
+      <x:c r="E64" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F64" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str"/>
+      <x:c r="B65" t="str"/>
+      <x:c r="C65" s="20" t="str"/>
+      <x:c r="D65" s="22"/>
+      <x:c r="E65" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F65" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str"/>
+      <x:c r="B66" t="str"/>
+      <x:c r="C66" s="20" t="str"/>
+      <x:c r="D66" s="22"/>
+      <x:c r="E66" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F66" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str"/>
+      <x:c r="B67" t="str"/>
+      <x:c r="C67" s="20" t="str"/>
+      <x:c r="D67" s="22"/>
+      <x:c r="E67" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F67" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str"/>
+      <x:c r="B68" t="str"/>
+      <x:c r="C68" s="20" t="str"/>
+      <x:c r="D68" s="22"/>
+      <x:c r="E68" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F68" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str"/>
+      <x:c r="B69" t="str"/>
+      <x:c r="C69" s="20" t="str"/>
+      <x:c r="D69" s="22"/>
+      <x:c r="E69" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F69" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str"/>
+      <x:c r="B70" t="str"/>
+      <x:c r="C70" s="20" t="str"/>
+      <x:c r="D70" s="22"/>
+      <x:c r="E70" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F70" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str"/>
+      <x:c r="B71" t="str"/>
+      <x:c r="C71" s="20" t="str"/>
+      <x:c r="D71" s="22"/>
+      <x:c r="E71" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F71" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str"/>
+      <x:c r="B72" t="str"/>
+      <x:c r="C72" s="20" t="str"/>
+      <x:c r="D72" s="22"/>
+      <x:c r="E72" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F72" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str"/>
+      <x:c r="B73" t="str"/>
+      <x:c r="C73" s="20" t="str"/>
+      <x:c r="D73" s="22"/>
+      <x:c r="E73" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F73" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str"/>
+      <x:c r="B74" t="str"/>
+      <x:c r="C74" s="20" t="str"/>
+      <x:c r="D74" s="22"/>
+      <x:c r="E74" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F74" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str"/>
+      <x:c r="B75" t="str"/>
+      <x:c r="C75" s="20" t="str"/>
+      <x:c r="D75" s="22"/>
+      <x:c r="E75" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F75" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str"/>
+      <x:c r="B76" t="str"/>
+      <x:c r="C76" s="20" t="str"/>
+      <x:c r="D76" s="22"/>
+      <x:c r="E76" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F76" t="str"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str"/>
+      <x:c r="B77" t="str"/>
+      <x:c r="C77" s="20" t="str"/>
+      <x:c r="D77" s="22"/>
+      <x:c r="E77" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F77" t="str"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str"/>
+      <x:c r="B78" t="str"/>
+      <x:c r="C78" s="20" t="str"/>
+      <x:c r="D78" s="22"/>
+      <x:c r="E78" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F78" t="str"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str"/>
+      <x:c r="B79" t="str"/>
+      <x:c r="C79" s="20" t="str"/>
+      <x:c r="D79" s="22"/>
+      <x:c r="E79" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F79" t="str"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str"/>
+      <x:c r="B80" t="str"/>
+      <x:c r="C80" s="20" t="str"/>
+      <x:c r="D80" s="22"/>
+      <x:c r="E80" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F80" t="str"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str"/>
+      <x:c r="B81" t="str"/>
+      <x:c r="C81" s="20" t="str"/>
+      <x:c r="D81" s="22"/>
+      <x:c r="E81" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F81" t="str"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str"/>
+      <x:c r="B82" t="str"/>
+      <x:c r="C82" s="20" t="str"/>
+      <x:c r="D82" s="22"/>
+      <x:c r="E82" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F82" t="str"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str"/>
+      <x:c r="B83" t="str"/>
+      <x:c r="C83" s="20" t="str"/>
+      <x:c r="D83" s="22"/>
+      <x:c r="E83" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F83" t="str"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str"/>
+      <x:c r="B84" t="str"/>
+      <x:c r="C84" s="20" t="str"/>
+      <x:c r="D84" s="22"/>
+      <x:c r="E84" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F84" t="str"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str"/>
+      <x:c r="B85" t="str"/>
+      <x:c r="C85" s="20" t="str"/>
+      <x:c r="D85" s="22"/>
+      <x:c r="E85" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F85" t="str"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str"/>
+      <x:c r="B86" t="str"/>
+      <x:c r="C86" s="20" t="str"/>
+      <x:c r="D86" s="22"/>
+      <x:c r="E86" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F86" t="str"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str"/>
+      <x:c r="B87" t="str"/>
+      <x:c r="C87" s="20" t="str"/>
+      <x:c r="D87" s="22"/>
+      <x:c r="E87" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F87" t="str"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str"/>
+      <x:c r="B88" t="str"/>
+      <x:c r="C88" s="20" t="str"/>
+      <x:c r="D88" s="22"/>
+      <x:c r="E88" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F88" t="str"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str"/>
+      <x:c r="B89" t="str"/>
+      <x:c r="C89" s="20" t="str"/>
+      <x:c r="D89" s="22"/>
+      <x:c r="E89" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F89" t="str"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str"/>
+      <x:c r="B90" t="str"/>
+      <x:c r="C90" s="20" t="str"/>
+      <x:c r="D90" s="22"/>
+      <x:c r="E90" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F90" t="str"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str"/>
+      <x:c r="B91" t="str"/>
+      <x:c r="C91" s="20" t="str"/>
+      <x:c r="D91" s="22"/>
+      <x:c r="E91" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F91" t="str"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str"/>
+      <x:c r="B92" t="str"/>
+      <x:c r="C92" s="20" t="str"/>
+      <x:c r="D92" s="22"/>
+      <x:c r="E92" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F92" t="str"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str"/>
+      <x:c r="B93" t="str"/>
+      <x:c r="C93" s="20" t="str"/>
+      <x:c r="D93" s="22"/>
+      <x:c r="E93" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F93" t="str"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str"/>
+      <x:c r="B94" t="str"/>
+      <x:c r="C94" s="20" t="str"/>
+      <x:c r="D94" s="22"/>
+      <x:c r="E94" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F94" t="str"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str"/>
+      <x:c r="B95" t="str"/>
+      <x:c r="C95" s="20" t="str"/>
+      <x:c r="D95" s="22"/>
+      <x:c r="E95" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F95" t="str"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str"/>
+      <x:c r="B96" t="str"/>
+      <x:c r="C96" s="20" t="str"/>
+      <x:c r="D96" s="22"/>
+      <x:c r="E96" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F96" t="str"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str"/>
+      <x:c r="B97" t="str"/>
+      <x:c r="C97" s="20" t="str"/>
+      <x:c r="D97" s="22"/>
+      <x:c r="E97" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F97" t="str"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str"/>
+      <x:c r="B98" t="str"/>
+      <x:c r="C98" s="20" t="str"/>
+      <x:c r="D98" s="22"/>
+      <x:c r="E98" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F98" t="str"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str"/>
+      <x:c r="B99" t="str"/>
+      <x:c r="C99" s="20" t="str"/>
+      <x:c r="D99" s="22"/>
+      <x:c r="E99" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F99" t="str"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str"/>
+      <x:c r="B100" t="str"/>
+      <x:c r="C100" s="20" t="str"/>
+      <x:c r="D100" s="22"/>
+      <x:c r="E100" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F100" t="str"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str"/>
+      <x:c r="B101" t="str"/>
+      <x:c r="C101" s="20" t="str"/>
+      <x:c r="D101" s="22"/>
+      <x:c r="E101" t="str">
+        <x:v>Hours</x:v>
+      </x:c>
+      <x:c r="F101" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="E2:E51">
+    <x:dataValidation type="list" sqref="E2:E101">
       <x:formula1>"Hours"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="F2:F51">
+    <x:dataValidation type="list" sqref="F2:F101">
       <x:formula1>"IND,ANZ"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa62fff52e314310"/>
+  </x:tableParts>
 </x:worksheet>
 </file>